--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_12-07-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_12-07-2025.xlsx
@@ -2645,7 +2645,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-cavity-insulation-cw4050-450mm-x-1200mm-pack-of-11 (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
